--- a/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SDC.xlsx
+++ b/site/leagues/proliga/2026_2027/xlsx/opponent_shooting_packs/opponent_shooting_pack_SDC.xlsx
@@ -933,7 +933,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -3237,7 +3241,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -4533,7 +4541,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -6585,7 +6597,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -8353,7 +8369,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -8447,7 +8467,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -8933,7 +8957,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -10071,7 +10099,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -10263,7 +10295,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>B. Oghene</t>
@@ -10749,7 +10785,11 @@
           <t>SDC_B._OGHENE</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>322155</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>B. Oghene</t>
